--- a/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{572BB0F1-85D2-474D-9619-583CC9E6DFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17CA7841-C4EB-465C-9981-8545E7961484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17CA7841-C4EB-465C-9981-8545E7961484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAECD1E6-C86F-406E-809D-6BE10F495E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="529">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -1009,6 +1009,12 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>w11285720-380</t>
+  </si>
+  <si>
+    <t>at grid node - w11285720-380</t>
+  </si>
+  <si>
     <t>w18629425-380</t>
   </si>
   <si>
@@ -1021,6 +1027,12 @@
     <t>at grid node - w22720647-380</t>
   </si>
   <si>
+    <t>w22766160-380</t>
+  </si>
+  <si>
+    <t>at grid node - w22766160-380</t>
+  </si>
+  <si>
     <t>w22767509-380</t>
   </si>
   <si>
@@ -1081,30 +1093,30 @@
     <t>at grid node - w24268944-380</t>
   </si>
   <si>
+    <t>w24604789-380</t>
+  </si>
+  <si>
+    <t>at grid node - w24604789-380</t>
+  </si>
+  <si>
+    <t>w24757392-380</t>
+  </si>
+  <si>
+    <t>at grid node - w24757392-380</t>
+  </si>
+  <si>
     <t>w24921206-380</t>
   </si>
   <si>
     <t>at grid node - w24921206-380</t>
   </si>
   <si>
-    <t>w25043127-380</t>
-  </si>
-  <si>
-    <t>at grid node - w25043127-380</t>
-  </si>
-  <si>
     <t>w25306752-380</t>
   </si>
   <si>
     <t>at grid node - w25306752-380</t>
   </si>
   <si>
-    <t>w25306938-380</t>
-  </si>
-  <si>
-    <t>at grid node - w25306938-380</t>
-  </si>
-  <si>
     <t>w25786404-380</t>
   </si>
   <si>
@@ -1129,12 +1141,6 @@
     <t>at grid node - w26383042-380</t>
   </si>
   <si>
-    <t>w26403575-380</t>
-  </si>
-  <si>
-    <t>at grid node - w26403575-380</t>
-  </si>
-  <si>
     <t>w26472665-380</t>
   </si>
   <si>
@@ -1153,6 +1159,18 @@
     <t>at grid node - w27149550-380</t>
   </si>
   <si>
+    <t>w28327356-380</t>
+  </si>
+  <si>
+    <t>at grid node - w28327356-380</t>
+  </si>
+  <si>
+    <t>w29713902-380</t>
+  </si>
+  <si>
+    <t>at grid node - w29713902-380</t>
+  </si>
+  <si>
     <t>w30040568-380</t>
   </si>
   <si>
@@ -1171,6 +1189,12 @@
     <t>at grid node - w30613895-380</t>
   </si>
   <si>
+    <t>w31131320-380</t>
+  </si>
+  <si>
+    <t>at grid node - w31131320-380</t>
+  </si>
+  <si>
     <t>w31131325-380</t>
   </si>
   <si>
@@ -1189,6 +1213,12 @@
     <t>at grid node - w32076853-380</t>
   </si>
   <si>
+    <t>w32472806-380</t>
+  </si>
+  <si>
+    <t>at grid node - w32472806-380</t>
+  </si>
+  <si>
     <t>w32904794-380</t>
   </si>
   <si>
@@ -1201,6 +1231,12 @@
     <t>at grid node - w33816726-380</t>
   </si>
   <si>
+    <t>w35763480-380</t>
+  </si>
+  <si>
+    <t>at grid node - w35763480-380</t>
+  </si>
+  <si>
     <t>w37764852-380</t>
   </si>
   <si>
@@ -1213,10 +1249,10 @@
     <t>at grid node - w38661452-380</t>
   </si>
   <si>
-    <t>w42049947-380</t>
-  </si>
-  <si>
-    <t>at grid node - w42049947-380</t>
+    <t>w41389594-380</t>
+  </si>
+  <si>
+    <t>at grid node - w41389594-380</t>
   </si>
   <si>
     <t>w42050342-380</t>
@@ -1225,6 +1261,12 @@
     <t>at grid node - w42050342-380</t>
   </si>
   <si>
+    <t>w42488850-380</t>
+  </si>
+  <si>
+    <t>at grid node - w42488850-380</t>
+  </si>
+  <si>
     <t>w42560068-380</t>
   </si>
   <si>
@@ -1237,12 +1279,36 @@
     <t>at grid node - w42736239-380</t>
   </si>
   <si>
+    <t>w42797575-380</t>
+  </si>
+  <si>
+    <t>at grid node - w42797575-380</t>
+  </si>
+  <si>
     <t>w43688805-380</t>
   </si>
   <si>
     <t>at grid node - w43688805-380</t>
   </si>
   <si>
+    <t>w691662101-380</t>
+  </si>
+  <si>
+    <t>at grid node - w691662101-380</t>
+  </si>
+  <si>
+    <t>w57727004-380</t>
+  </si>
+  <si>
+    <t>at grid node - w57727004-380</t>
+  </si>
+  <si>
+    <t>w59026005-380</t>
+  </si>
+  <si>
+    <t>at grid node - w59026005-380</t>
+  </si>
+  <si>
     <t>w78441561-380</t>
   </si>
   <si>
@@ -1261,36 +1327,72 @@
     <t>at grid node - w92165128-380</t>
   </si>
   <si>
+    <t>w108797675-380</t>
+  </si>
+  <si>
+    <t>at grid node - w108797675-380</t>
+  </si>
+  <si>
+    <t>w954305865-380</t>
+  </si>
+  <si>
+    <t>at grid node - w954305865-380</t>
+  </si>
+  <si>
+    <t>w143854536-380</t>
+  </si>
+  <si>
+    <t>at grid node - w143854536-380</t>
+  </si>
+  <si>
     <t>w143882655-380</t>
   </si>
   <si>
     <t>at grid node - w143882655-380</t>
   </si>
   <si>
-    <t>w147521567-380</t>
-  </si>
-  <si>
-    <t>at grid node - w147521567-380</t>
-  </si>
-  <si>
     <t>w148446247-380</t>
   </si>
   <si>
     <t>at grid node - w148446247-380</t>
   </si>
   <si>
+    <t>w149256409-380</t>
+  </si>
+  <si>
+    <t>at grid node - w149256409-380</t>
+  </si>
+  <si>
     <t>w152107815-380</t>
   </si>
   <si>
     <t>at grid node - w152107815-380</t>
   </si>
   <si>
+    <t>w152403632-380</t>
+  </si>
+  <si>
+    <t>at grid node - w152403632-380</t>
+  </si>
+  <si>
+    <t>w156673636-380</t>
+  </si>
+  <si>
+    <t>at grid node - w156673636-380</t>
+  </si>
+  <si>
     <t>w156960655-380</t>
   </si>
   <si>
     <t>at grid node - w156960655-380</t>
   </si>
   <si>
+    <t>w157328339-380</t>
+  </si>
+  <si>
+    <t>at grid node - w157328339-380</t>
+  </si>
+  <si>
     <t>w160584794-380</t>
   </si>
   <si>
@@ -1315,28 +1417,16 @@
     <t>at grid node - w202747445-380</t>
   </si>
   <si>
-    <t>w207248812-380</t>
-  </si>
-  <si>
-    <t>at grid node - w207248812-380</t>
-  </si>
-  <si>
     <t>w87653464-380</t>
   </si>
   <si>
     <t>at grid node - w87653464-380</t>
   </si>
   <si>
-    <t>w259561755-380</t>
-  </si>
-  <si>
-    <t>at grid node - w259561755-380</t>
-  </si>
-  <si>
-    <t>w940470389-380</t>
-  </si>
-  <si>
-    <t>at grid node - w940470389-380</t>
+    <t>w395847307-380</t>
+  </si>
+  <si>
+    <t>at grid node - w395847307-380</t>
   </si>
   <si>
     <t>w941453716-380</t>
@@ -1345,12 +1435,24 @@
     <t>at grid node - w941453716-380</t>
   </si>
   <si>
+    <t>w941805476-380</t>
+  </si>
+  <si>
+    <t>at grid node - w941805476-380</t>
+  </si>
+  <si>
     <t>w942771541-380</t>
   </si>
   <si>
     <t>at grid node - w942771541-380</t>
   </si>
   <si>
+    <t>w946206351-380</t>
+  </si>
+  <si>
+    <t>at grid node - w946206351-380</t>
+  </si>
+  <si>
     <t>w948341123-380</t>
   </si>
   <si>
@@ -1381,6 +1483,24 @@
     <t>at grid node - w1128250704-380</t>
   </si>
   <si>
+    <t>DE176-380</t>
+  </si>
+  <si>
+    <t>at grid node - DE176-380</t>
+  </si>
+  <si>
+    <t>DE143-380</t>
+  </si>
+  <si>
+    <t>at grid node - DE143-380</t>
+  </si>
+  <si>
+    <t>DE170-380</t>
+  </si>
+  <si>
+    <t>at grid node - DE170-380</t>
+  </si>
+  <si>
     <t>DE68-380</t>
   </si>
   <si>
@@ -1399,6 +1519,12 @@
     <t>at grid node - DE227-380</t>
   </si>
   <si>
+    <t>DE230-380</t>
+  </si>
+  <si>
+    <t>at grid node - DE230-380</t>
+  </si>
+  <si>
     <t>w42861703-380</t>
   </si>
   <si>
@@ -1435,18 +1561,18 @@
     <t>at grid node - DE134-380</t>
   </si>
   <si>
-    <t>DE180-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE180-380</t>
-  </si>
-  <si>
     <t>DE221-380</t>
   </si>
   <si>
     <t>at grid node - DE221-380</t>
   </si>
   <si>
+    <t>DE124-380</t>
+  </si>
+  <si>
+    <t>at grid node - DE124-380</t>
+  </si>
+  <si>
     <t>DE135-380</t>
   </si>
   <si>
@@ -1465,6 +1591,12 @@
     <t>at grid node - DE214-380</t>
   </si>
   <si>
+    <t>DE57-380</t>
+  </si>
+  <si>
+    <t>at grid node - DE57-380</t>
+  </si>
+  <si>
     <t>DE69-380</t>
   </si>
   <si>
@@ -1483,58 +1615,16 @@
     <t>at grid node - DE217-380</t>
   </si>
   <si>
-    <t>DE49-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE49-380</t>
-  </si>
-  <si>
-    <t>DE63-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE63-380</t>
-  </si>
-  <si>
     <t>DE140-380</t>
   </si>
   <si>
     <t>at grid node - DE140-380</t>
   </si>
   <si>
-    <t>w89043564-380</t>
-  </si>
-  <si>
-    <t>at grid node - w89043564-380</t>
-  </si>
-  <si>
-    <t>DE142-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE142-380</t>
-  </si>
-  <si>
-    <t>DE138-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE138-380</t>
-  </si>
-  <si>
     <t>DE209-380</t>
   </si>
   <si>
     <t>at grid node - DE209-380</t>
-  </si>
-  <si>
-    <t>DE52-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE52-380</t>
-  </si>
-  <si>
-    <t>w87653464-400</t>
-  </si>
-  <si>
-    <t>at grid node - w87653464-400</t>
   </si>
 </sst>
 </file>
@@ -1862,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T154"/>
+  <dimension ref="B3:T170"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
@@ -2141,10 +2231,10 @@
         <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>150</v>
+        <v>327</v>
       </c>
       <c r="S14" t="s">
-        <v>151</v>
+        <v>328</v>
       </c>
       <c r="T14" t="s">
         <v>322</v>
@@ -2191,10 +2281,10 @@
         <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="T15" t="s">
         <v>322</v>
@@ -2241,10 +2331,10 @@
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="S16" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
       <c r="T16" t="s">
         <v>322</v>
@@ -2291,10 +2381,10 @@
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>329</v>
+        <v>190</v>
       </c>
       <c r="S17" t="s">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="T17" t="s">
         <v>322</v>
@@ -2341,10 +2431,10 @@
         <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="S18" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T18" t="s">
         <v>322</v>
@@ -2391,10 +2481,10 @@
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="T19" t="s">
         <v>322</v>
@@ -2441,10 +2531,10 @@
         <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="S20" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T20" t="s">
         <v>322</v>
@@ -2491,10 +2581,10 @@
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="S21" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="T21" t="s">
         <v>322</v>
@@ -2541,10 +2631,10 @@
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>192</v>
+        <v>341</v>
       </c>
       <c r="S22" t="s">
-        <v>193</v>
+        <v>342</v>
       </c>
       <c r="T22" t="s">
         <v>322</v>
@@ -2591,10 +2681,10 @@
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="S23" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="T23" t="s">
         <v>322</v>
@@ -2641,10 +2731,10 @@
         <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>339</v>
+        <v>122</v>
       </c>
       <c r="S24" t="s">
-        <v>340</v>
+        <v>123</v>
       </c>
       <c r="T24" t="s">
         <v>322</v>
@@ -2691,10 +2781,10 @@
         <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T25" t="s">
         <v>322</v>
@@ -2741,10 +2831,10 @@
         <v>78</v>
       </c>
       <c r="R26" t="s">
-        <v>146</v>
+        <v>345</v>
       </c>
       <c r="S26" t="s">
-        <v>147</v>
+        <v>346</v>
       </c>
       <c r="T26" t="s">
         <v>322</v>
@@ -2791,10 +2881,10 @@
         <v>78</v>
       </c>
       <c r="R27" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="S27" t="s">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="T27" t="s">
         <v>322</v>
@@ -2841,10 +2931,10 @@
         <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>343</v>
+        <v>202</v>
       </c>
       <c r="S28" t="s">
-        <v>344</v>
+        <v>203</v>
       </c>
       <c r="T28" t="s">
         <v>322</v>
@@ -2891,10 +2981,10 @@
         <v>78</v>
       </c>
       <c r="R29" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S29" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="T29" t="s">
         <v>322</v>
@@ -2941,10 +3031,10 @@
         <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="S30" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="T30" t="s">
         <v>322</v>
@@ -2991,10 +3081,10 @@
         <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="S31" t="s">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="T31" t="s">
         <v>322</v>
@@ -3041,10 +3131,10 @@
         <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>118</v>
+        <v>314</v>
       </c>
       <c r="S32" t="s">
-        <v>119</v>
+        <v>315</v>
       </c>
       <c r="T32" t="s">
         <v>322</v>
@@ -3091,10 +3181,10 @@
         <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="S33" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="T33" t="s">
         <v>322</v>
@@ -3141,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>349</v>
+        <v>90</v>
       </c>
       <c r="S34" t="s">
-        <v>350</v>
+        <v>91</v>
       </c>
       <c r="T34" t="s">
         <v>322</v>
@@ -3191,10 +3281,10 @@
         <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>284</v>
+        <v>118</v>
       </c>
       <c r="S35" t="s">
-        <v>285</v>
+        <v>119</v>
       </c>
       <c r="T35" t="s">
         <v>322</v>
@@ -3241,10 +3331,10 @@
         <v>78</v>
       </c>
       <c r="R36" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="S36" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T36" t="s">
         <v>322</v>
@@ -3279,10 +3369,10 @@
         <v>78</v>
       </c>
       <c r="R37" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="S37" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="T37" t="s">
         <v>322</v>
@@ -3317,10 +3407,10 @@
         <v>78</v>
       </c>
       <c r="R38" t="s">
-        <v>355</v>
+        <v>284</v>
       </c>
       <c r="S38" t="s">
-        <v>356</v>
+        <v>285</v>
       </c>
       <c r="T38" t="s">
         <v>322</v>
@@ -3393,10 +3483,10 @@
         <v>78</v>
       </c>
       <c r="R40" t="s">
-        <v>234</v>
+        <v>359</v>
       </c>
       <c r="S40" t="s">
-        <v>235</v>
+        <v>360</v>
       </c>
       <c r="T40" t="s">
         <v>322</v>
@@ -3431,10 +3521,10 @@
         <v>78</v>
       </c>
       <c r="R41" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="S41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T41" t="s">
         <v>322</v>
@@ -3469,10 +3559,10 @@
         <v>78</v>
       </c>
       <c r="R42" t="s">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="S42" t="s">
-        <v>362</v>
+        <v>235</v>
       </c>
       <c r="T42" t="s">
         <v>322</v>
@@ -3621,10 +3711,10 @@
         <v>78</v>
       </c>
       <c r="R46" t="s">
-        <v>230</v>
+        <v>369</v>
       </c>
       <c r="S46" t="s">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="T46" t="s">
         <v>322</v>
@@ -3697,10 +3787,10 @@
         <v>78</v>
       </c>
       <c r="R48" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="S48" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="T48" t="s">
         <v>322</v>
@@ -3735,10 +3825,10 @@
         <v>78</v>
       </c>
       <c r="R49" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
       <c r="S49" t="s">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="T49" t="s">
         <v>322</v>
@@ -3773,10 +3863,10 @@
         <v>78</v>
       </c>
       <c r="R50" t="s">
-        <v>290</v>
+        <v>373</v>
       </c>
       <c r="S50" t="s">
-        <v>291</v>
+        <v>374</v>
       </c>
       <c r="T50" t="s">
         <v>322</v>
@@ -3811,10 +3901,10 @@
         <v>78</v>
       </c>
       <c r="R51" t="s">
-        <v>132</v>
+        <v>251</v>
       </c>
       <c r="S51" t="s">
-        <v>133</v>
+        <v>252</v>
       </c>
       <c r="T51" t="s">
         <v>322</v>
@@ -3849,10 +3939,10 @@
         <v>78</v>
       </c>
       <c r="R52" t="s">
-        <v>371</v>
+        <v>290</v>
       </c>
       <c r="S52" t="s">
-        <v>372</v>
+        <v>291</v>
       </c>
       <c r="T52" t="s">
         <v>322</v>
@@ -3887,10 +3977,10 @@
         <v>78</v>
       </c>
       <c r="R53" t="s">
-        <v>373</v>
+        <v>132</v>
       </c>
       <c r="S53" t="s">
-        <v>374</v>
+        <v>133</v>
       </c>
       <c r="T53" t="s">
         <v>322</v>
@@ -3925,10 +4015,10 @@
         <v>78</v>
       </c>
       <c r="R54" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="S54" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="T54" t="s">
         <v>322</v>
@@ -4077,10 +4167,10 @@
         <v>78</v>
       </c>
       <c r="R58" t="s">
-        <v>381</v>
+        <v>96</v>
       </c>
       <c r="S58" t="s">
-        <v>382</v>
+        <v>97</v>
       </c>
       <c r="T58" t="s">
         <v>322</v>
@@ -4115,10 +4205,10 @@
         <v>78</v>
       </c>
       <c r="R59" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="S59" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="T59" t="s">
         <v>322</v>
@@ -4153,10 +4243,10 @@
         <v>78</v>
       </c>
       <c r="R60" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="S60" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="T60" t="s">
         <v>322</v>
@@ -4191,10 +4281,10 @@
         <v>78</v>
       </c>
       <c r="R61" t="s">
-        <v>144</v>
+        <v>385</v>
       </c>
       <c r="S61" t="s">
-        <v>145</v>
+        <v>386</v>
       </c>
       <c r="T61" t="s">
         <v>322</v>
@@ -4229,10 +4319,10 @@
         <v>78</v>
       </c>
       <c r="R62" t="s">
-        <v>88</v>
+        <v>387</v>
       </c>
       <c r="S62" t="s">
-        <v>89</v>
+        <v>388</v>
       </c>
       <c r="T62" t="s">
         <v>322</v>
@@ -4267,10 +4357,10 @@
         <v>78</v>
       </c>
       <c r="R63" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="S63" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="T63" t="s">
         <v>322</v>
@@ -4305,10 +4395,10 @@
         <v>78</v>
       </c>
       <c r="R64" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="S64" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="T64" t="s">
         <v>322</v>
@@ -4343,10 +4433,10 @@
         <v>78</v>
       </c>
       <c r="R65" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="S65" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="T65" t="s">
         <v>322</v>
@@ -4381,10 +4471,10 @@
         <v>78</v>
       </c>
       <c r="R66" t="s">
-        <v>393</v>
+        <v>288</v>
       </c>
       <c r="S66" t="s">
-        <v>394</v>
+        <v>289</v>
       </c>
       <c r="T66" t="s">
         <v>322</v>
@@ -4419,10 +4509,10 @@
         <v>78</v>
       </c>
       <c r="R67" t="s">
-        <v>188</v>
+        <v>395</v>
       </c>
       <c r="S67" t="s">
-        <v>189</v>
+        <v>396</v>
       </c>
       <c r="T67" t="s">
         <v>322</v>
@@ -4457,10 +4547,10 @@
         <v>78</v>
       </c>
       <c r="R68" t="s">
-        <v>395</v>
+        <v>144</v>
       </c>
       <c r="S68" t="s">
-        <v>396</v>
+        <v>145</v>
       </c>
       <c r="T68" t="s">
         <v>322</v>
@@ -4533,10 +4623,10 @@
         <v>78</v>
       </c>
       <c r="R70" t="s">
-        <v>267</v>
+        <v>88</v>
       </c>
       <c r="S70" t="s">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="T70" t="s">
         <v>322</v>
@@ -4609,10 +4699,10 @@
         <v>78</v>
       </c>
       <c r="R72" t="s">
-        <v>172</v>
+        <v>401</v>
       </c>
       <c r="S72" t="s">
-        <v>173</v>
+        <v>402</v>
       </c>
       <c r="T72" t="s">
         <v>322</v>
@@ -4647,10 +4737,10 @@
         <v>78</v>
       </c>
       <c r="R73" t="s">
-        <v>280</v>
+        <v>403</v>
       </c>
       <c r="S73" t="s">
-        <v>281</v>
+        <v>404</v>
       </c>
       <c r="T73" t="s">
         <v>322</v>
@@ -4685,10 +4775,10 @@
         <v>78</v>
       </c>
       <c r="R74" t="s">
-        <v>198</v>
+        <v>405</v>
       </c>
       <c r="S74" t="s">
-        <v>199</v>
+        <v>406</v>
       </c>
       <c r="T74" t="s">
         <v>322</v>
@@ -4723,10 +4813,10 @@
         <v>78</v>
       </c>
       <c r="R75" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="S75" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="T75" t="s">
         <v>322</v>
@@ -4761,10 +4851,10 @@
         <v>78</v>
       </c>
       <c r="R76" t="s">
-        <v>166</v>
+        <v>407</v>
       </c>
       <c r="S76" t="s">
-        <v>167</v>
+        <v>408</v>
       </c>
       <c r="T76" t="s">
         <v>322</v>
@@ -4799,10 +4889,10 @@
         <v>78</v>
       </c>
       <c r="R77" t="s">
-        <v>269</v>
+        <v>409</v>
       </c>
       <c r="S77" t="s">
-        <v>270</v>
+        <v>410</v>
       </c>
       <c r="T77" t="s">
         <v>322</v>
@@ -4837,10 +4927,10 @@
         <v>78</v>
       </c>
       <c r="R78" t="s">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="S78" t="s">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="T78" t="s">
         <v>322</v>
@@ -4875,10 +4965,10 @@
         <v>78</v>
       </c>
       <c r="R79" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="S79" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="T79" t="s">
         <v>322</v>
@@ -4913,10 +5003,10 @@
         <v>78</v>
       </c>
       <c r="R80" t="s">
-        <v>403</v>
+        <v>267</v>
       </c>
       <c r="S80" t="s">
-        <v>404</v>
+        <v>268</v>
       </c>
       <c r="T80" t="s">
         <v>322</v>
@@ -4951,10 +5041,10 @@
         <v>78</v>
       </c>
       <c r="R81" t="s">
-        <v>100</v>
+        <v>415</v>
       </c>
       <c r="S81" t="s">
-        <v>101</v>
+        <v>416</v>
       </c>
       <c r="T81" t="s">
         <v>322</v>
@@ -4989,10 +5079,10 @@
         <v>78</v>
       </c>
       <c r="R82" t="s">
-        <v>405</v>
+        <v>172</v>
       </c>
       <c r="S82" t="s">
-        <v>406</v>
+        <v>173</v>
       </c>
       <c r="T82" t="s">
         <v>322</v>
@@ -5027,10 +5117,10 @@
         <v>78</v>
       </c>
       <c r="R83" t="s">
-        <v>310</v>
+        <v>417</v>
       </c>
       <c r="S83" t="s">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="T83" t="s">
         <v>322</v>
@@ -5065,10 +5155,10 @@
         <v>78</v>
       </c>
       <c r="R84" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="S84" t="s">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="T84" t="s">
         <v>322</v>
@@ -5103,10 +5193,10 @@
         <v>78</v>
       </c>
       <c r="R85" t="s">
-        <v>407</v>
+        <v>198</v>
       </c>
       <c r="S85" t="s">
-        <v>408</v>
+        <v>199</v>
       </c>
       <c r="T85" t="s">
         <v>322</v>
@@ -5141,10 +5231,10 @@
         <v>78</v>
       </c>
       <c r="R86" t="s">
-        <v>409</v>
+        <v>86</v>
       </c>
       <c r="S86" t="s">
-        <v>410</v>
+        <v>87</v>
       </c>
       <c r="T86" t="s">
         <v>322</v>
@@ -5179,10 +5269,10 @@
         <v>78</v>
       </c>
       <c r="R87" t="s">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="S87" t="s">
-        <v>141</v>
+        <v>420</v>
       </c>
       <c r="T87" t="s">
         <v>322</v>
@@ -5217,10 +5307,10 @@
         <v>78</v>
       </c>
       <c r="R88" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="S88" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="T88" t="s">
         <v>322</v>
@@ -5243,10 +5333,10 @@
         <v>78</v>
       </c>
       <c r="R89" t="s">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="S89" t="s">
-        <v>287</v>
+        <v>167</v>
       </c>
       <c r="T89" t="s">
         <v>322</v>
@@ -5269,10 +5359,10 @@
         <v>78</v>
       </c>
       <c r="R90" t="s">
-        <v>413</v>
+        <v>269</v>
       </c>
       <c r="S90" t="s">
-        <v>414</v>
+        <v>270</v>
       </c>
       <c r="T90" t="s">
         <v>322</v>
@@ -5295,10 +5385,10 @@
         <v>78</v>
       </c>
       <c r="R91" t="s">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="S91" t="s">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="T91" t="s">
         <v>322</v>
@@ -5321,10 +5411,10 @@
         <v>78</v>
       </c>
       <c r="R92" t="s">
-        <v>212</v>
+        <v>423</v>
       </c>
       <c r="S92" t="s">
-        <v>213</v>
+        <v>424</v>
       </c>
       <c r="T92" t="s">
         <v>322</v>
@@ -5347,10 +5437,10 @@
         <v>78</v>
       </c>
       <c r="R93" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="S93" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="T93" t="s">
         <v>322</v>
@@ -5373,10 +5463,10 @@
         <v>78</v>
       </c>
       <c r="R94" t="s">
-        <v>417</v>
+        <v>100</v>
       </c>
       <c r="S94" t="s">
-        <v>418</v>
+        <v>101</v>
       </c>
       <c r="T94" t="s">
         <v>322</v>
@@ -5399,10 +5489,10 @@
         <v>78</v>
       </c>
       <c r="R95" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="S95" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="T95" t="s">
         <v>322</v>
@@ -5425,10 +5515,10 @@
         <v>78</v>
       </c>
       <c r="R96" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="S96" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="T96" t="s">
         <v>322</v>
@@ -5451,10 +5541,10 @@
         <v>78</v>
       </c>
       <c r="R97" t="s">
-        <v>214</v>
+        <v>431</v>
       </c>
       <c r="S97" t="s">
-        <v>215</v>
+        <v>432</v>
       </c>
       <c r="T97" t="s">
         <v>322</v>
@@ -5477,10 +5567,10 @@
         <v>78</v>
       </c>
       <c r="R98" t="s">
-        <v>423</v>
+        <v>310</v>
       </c>
       <c r="S98" t="s">
-        <v>424</v>
+        <v>311</v>
       </c>
       <c r="T98" t="s">
         <v>322</v>
@@ -5503,10 +5593,10 @@
         <v>78</v>
       </c>
       <c r="R99" t="s">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="S99" t="s">
-        <v>426</v>
+        <v>137</v>
       </c>
       <c r="T99" t="s">
         <v>322</v>
@@ -5529,10 +5619,10 @@
         <v>78</v>
       </c>
       <c r="R100" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="S100" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="T100" t="s">
         <v>322</v>
@@ -5555,10 +5645,10 @@
         <v>78</v>
       </c>
       <c r="R101" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="S101" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="T101" t="s">
         <v>322</v>
@@ -5581,10 +5671,10 @@
         <v>78</v>
       </c>
       <c r="R102" t="s">
-        <v>156</v>
+        <v>437</v>
       </c>
       <c r="S102" t="s">
-        <v>157</v>
+        <v>438</v>
       </c>
       <c r="T102" t="s">
         <v>322</v>
@@ -5607,10 +5697,10 @@
         <v>78</v>
       </c>
       <c r="R103" t="s">
-        <v>116</v>
+        <v>439</v>
       </c>
       <c r="S103" t="s">
-        <v>117</v>
+        <v>440</v>
       </c>
       <c r="T103" t="s">
         <v>322</v>
@@ -5633,10 +5723,10 @@
         <v>78</v>
       </c>
       <c r="R104" t="s">
-        <v>134</v>
+        <v>286</v>
       </c>
       <c r="S104" t="s">
-        <v>135</v>
+        <v>287</v>
       </c>
       <c r="T104" t="s">
         <v>322</v>
@@ -5659,10 +5749,10 @@
         <v>78</v>
       </c>
       <c r="R105" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="S105" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="T105" t="s">
         <v>322</v>
@@ -5685,10 +5775,10 @@
         <v>78</v>
       </c>
       <c r="R106" t="s">
-        <v>433</v>
+        <v>176</v>
       </c>
       <c r="S106" t="s">
-        <v>434</v>
+        <v>177</v>
       </c>
       <c r="T106" t="s">
         <v>322</v>
@@ -5711,10 +5801,10 @@
         <v>78</v>
       </c>
       <c r="R107" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="S107" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="T107" t="s">
         <v>322</v>
@@ -5737,10 +5827,10 @@
         <v>78</v>
       </c>
       <c r="R108" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="S108" t="s">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="T108" t="s">
         <v>322</v>
@@ -5763,10 +5853,10 @@
         <v>78</v>
       </c>
       <c r="R109" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="S109" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="T109" t="s">
         <v>322</v>
@@ -5789,10 +5879,10 @@
         <v>78</v>
       </c>
       <c r="R110" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="S110" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="T110" t="s">
         <v>322</v>
@@ -5815,10 +5905,10 @@
         <v>78</v>
       </c>
       <c r="R111" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="S111" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="T111" t="s">
         <v>322</v>
@@ -5841,10 +5931,10 @@
         <v>78</v>
       </c>
       <c r="R112" t="s">
-        <v>304</v>
+        <v>451</v>
       </c>
       <c r="S112" t="s">
-        <v>305</v>
+        <v>452</v>
       </c>
       <c r="T112" t="s">
         <v>322</v>
@@ -5867,10 +5957,10 @@
         <v>78</v>
       </c>
       <c r="R113" t="s">
-        <v>312</v>
+        <v>453</v>
       </c>
       <c r="S113" t="s">
-        <v>313</v>
+        <v>454</v>
       </c>
       <c r="T113" t="s">
         <v>322</v>
@@ -5893,10 +5983,10 @@
         <v>78</v>
       </c>
       <c r="R114" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="S114" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="T114" t="s">
         <v>322</v>
@@ -5919,10 +6009,10 @@
         <v>78</v>
       </c>
       <c r="R115" t="s">
-        <v>130</v>
+        <v>457</v>
       </c>
       <c r="S115" t="s">
-        <v>131</v>
+        <v>458</v>
       </c>
       <c r="T115" t="s">
         <v>322</v>
@@ -5945,10 +6035,10 @@
         <v>78</v>
       </c>
       <c r="R116" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="S116" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="T116" t="s">
         <v>322</v>
@@ -5971,10 +6061,10 @@
         <v>78</v>
       </c>
       <c r="R117" t="s">
-        <v>124</v>
+        <v>461</v>
       </c>
       <c r="S117" t="s">
-        <v>125</v>
+        <v>462</v>
       </c>
       <c r="T117" t="s">
         <v>322</v>
@@ -5997,10 +6087,10 @@
         <v>78</v>
       </c>
       <c r="R118" t="s">
-        <v>447</v>
+        <v>156</v>
       </c>
       <c r="S118" t="s">
-        <v>448</v>
+        <v>157</v>
       </c>
       <c r="T118" t="s">
         <v>322</v>
@@ -6023,10 +6113,10 @@
         <v>78</v>
       </c>
       <c r="R119" t="s">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="S119" t="s">
-        <v>163</v>
+        <v>317</v>
       </c>
       <c r="T119" t="s">
         <v>322</v>
@@ -6049,10 +6139,10 @@
         <v>78</v>
       </c>
       <c r="R120" t="s">
-        <v>449</v>
+        <v>164</v>
       </c>
       <c r="S120" t="s">
-        <v>450</v>
+        <v>165</v>
       </c>
       <c r="T120" t="s">
         <v>322</v>
@@ -6075,10 +6165,10 @@
         <v>78</v>
       </c>
       <c r="R121" t="s">
-        <v>451</v>
+        <v>245</v>
       </c>
       <c r="S121" t="s">
-        <v>452</v>
+        <v>246</v>
       </c>
       <c r="T121" t="s">
         <v>322</v>
@@ -6101,10 +6191,10 @@
         <v>78</v>
       </c>
       <c r="R122" t="s">
-        <v>453</v>
+        <v>134</v>
       </c>
       <c r="S122" t="s">
-        <v>454</v>
+        <v>135</v>
       </c>
       <c r="T122" t="s">
         <v>322</v>
@@ -6127,10 +6217,10 @@
         <v>78</v>
       </c>
       <c r="R123" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="S123" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="T123" t="s">
         <v>322</v>
@@ -6153,10 +6243,10 @@
         <v>78</v>
       </c>
       <c r="R124" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="S124" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="T124" t="s">
         <v>322</v>
@@ -6179,10 +6269,10 @@
         <v>78</v>
       </c>
       <c r="R125" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="S125" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="T125" t="s">
         <v>322</v>
@@ -6205,10 +6295,10 @@
         <v>78</v>
       </c>
       <c r="R126" t="s">
-        <v>461</v>
+        <v>98</v>
       </c>
       <c r="S126" t="s">
-        <v>462</v>
+        <v>99</v>
       </c>
       <c r="T126" t="s">
         <v>322</v>
@@ -6231,10 +6321,10 @@
         <v>78</v>
       </c>
       <c r="R127" t="s">
-        <v>463</v>
+        <v>102</v>
       </c>
       <c r="S127" t="s">
-        <v>464</v>
+        <v>103</v>
       </c>
       <c r="T127" t="s">
         <v>322</v>
@@ -6257,10 +6347,10 @@
         <v>78</v>
       </c>
       <c r="R128" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="S128" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="T128" t="s">
         <v>322</v>
@@ -6283,10 +6373,10 @@
         <v>78</v>
       </c>
       <c r="R129" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="S129" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="T129" t="s">
         <v>322</v>
@@ -6309,10 +6399,10 @@
         <v>78</v>
       </c>
       <c r="R130" t="s">
-        <v>306</v>
+        <v>473</v>
       </c>
       <c r="S130" t="s">
-        <v>307</v>
+        <v>474</v>
       </c>
       <c r="T130" t="s">
         <v>322</v>
@@ -6323,10 +6413,10 @@
         <v>78</v>
       </c>
       <c r="R131" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="S131" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="T131" t="s">
         <v>322</v>
@@ -6337,10 +6427,10 @@
         <v>78</v>
       </c>
       <c r="R132" t="s">
-        <v>471</v>
+        <v>304</v>
       </c>
       <c r="S132" t="s">
-        <v>472</v>
+        <v>305</v>
       </c>
       <c r="T132" t="s">
         <v>322</v>
@@ -6351,10 +6441,10 @@
         <v>78</v>
       </c>
       <c r="R133" t="s">
-        <v>473</v>
+        <v>312</v>
       </c>
       <c r="S133" t="s">
-        <v>474</v>
+        <v>313</v>
       </c>
       <c r="T133" t="s">
         <v>322</v>
@@ -6365,10 +6455,10 @@
         <v>78</v>
       </c>
       <c r="R134" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="S134" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="T134" t="s">
         <v>322</v>
@@ -6379,10 +6469,10 @@
         <v>78</v>
       </c>
       <c r="R135" t="s">
-        <v>142</v>
+        <v>479</v>
       </c>
       <c r="S135" t="s">
-        <v>143</v>
+        <v>480</v>
       </c>
       <c r="T135" t="s">
         <v>322</v>
@@ -6393,10 +6483,10 @@
         <v>78</v>
       </c>
       <c r="R136" t="s">
-        <v>477</v>
+        <v>124</v>
       </c>
       <c r="S136" t="s">
-        <v>478</v>
+        <v>125</v>
       </c>
       <c r="T136" t="s">
         <v>322</v>
@@ -6407,10 +6497,10 @@
         <v>78</v>
       </c>
       <c r="R137" t="s">
-        <v>302</v>
+        <v>481</v>
       </c>
       <c r="S137" t="s">
-        <v>303</v>
+        <v>482</v>
       </c>
       <c r="T137" t="s">
         <v>322</v>
@@ -6421,10 +6511,10 @@
         <v>78</v>
       </c>
       <c r="R138" t="s">
-        <v>148</v>
+        <v>483</v>
       </c>
       <c r="S138" t="s">
-        <v>149</v>
+        <v>484</v>
       </c>
       <c r="T138" t="s">
         <v>322</v>
@@ -6435,10 +6525,10 @@
         <v>78</v>
       </c>
       <c r="R139" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="S139" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="T139" t="s">
         <v>322</v>
@@ -6449,10 +6539,10 @@
         <v>78</v>
       </c>
       <c r="R140" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="S140" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="T140" t="s">
         <v>322</v>
@@ -6463,10 +6553,10 @@
         <v>78</v>
       </c>
       <c r="R141" t="s">
-        <v>483</v>
+        <v>162</v>
       </c>
       <c r="S141" t="s">
-        <v>484</v>
+        <v>163</v>
       </c>
       <c r="T141" t="s">
         <v>322</v>
@@ -6477,10 +6567,10 @@
         <v>78</v>
       </c>
       <c r="R142" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="S142" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="T142" t="s">
         <v>322</v>
@@ -6491,10 +6581,10 @@
         <v>78</v>
       </c>
       <c r="R143" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="S143" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="T143" t="s">
         <v>322</v>
@@ -6505,10 +6595,10 @@
         <v>78</v>
       </c>
       <c r="R144" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="S144" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="T144" t="s">
         <v>322</v>
@@ -6519,10 +6609,10 @@
         <v>78</v>
       </c>
       <c r="R145" t="s">
-        <v>152</v>
+        <v>495</v>
       </c>
       <c r="S145" t="s">
-        <v>153</v>
+        <v>496</v>
       </c>
       <c r="T145" t="s">
         <v>322</v>
@@ -6533,10 +6623,10 @@
         <v>78</v>
       </c>
       <c r="R146" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="S146" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="T146" t="s">
         <v>322</v>
@@ -6547,10 +6637,10 @@
         <v>78</v>
       </c>
       <c r="R147" t="s">
-        <v>226</v>
+        <v>499</v>
       </c>
       <c r="S147" t="s">
-        <v>227</v>
+        <v>500</v>
       </c>
       <c r="T147" t="s">
         <v>322</v>
@@ -6561,10 +6651,10 @@
         <v>78</v>
       </c>
       <c r="R148" t="s">
-        <v>308</v>
+        <v>501</v>
       </c>
       <c r="S148" t="s">
-        <v>309</v>
+        <v>502</v>
       </c>
       <c r="T148" t="s">
         <v>322</v>
@@ -6575,10 +6665,10 @@
         <v>78</v>
       </c>
       <c r="R149" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="S149" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="T149" t="s">
         <v>322</v>
@@ -6589,10 +6679,10 @@
         <v>78</v>
       </c>
       <c r="R150" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="S150" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="T150" t="s">
         <v>322</v>
@@ -6603,10 +6693,10 @@
         <v>78</v>
       </c>
       <c r="R151" t="s">
-        <v>170</v>
+        <v>507</v>
       </c>
       <c r="S151" t="s">
-        <v>171</v>
+        <v>508</v>
       </c>
       <c r="T151" t="s">
         <v>322</v>
@@ -6617,10 +6707,10 @@
         <v>78</v>
       </c>
       <c r="R152" t="s">
-        <v>497</v>
+        <v>306</v>
       </c>
       <c r="S152" t="s">
-        <v>498</v>
+        <v>307</v>
       </c>
       <c r="T152" t="s">
         <v>322</v>
@@ -6631,10 +6721,10 @@
         <v>78</v>
       </c>
       <c r="R153" t="s">
-        <v>108</v>
+        <v>509</v>
       </c>
       <c r="S153" t="s">
-        <v>109</v>
+        <v>510</v>
       </c>
       <c r="T153" t="s">
         <v>322</v>
@@ -6645,12 +6735,236 @@
         <v>78</v>
       </c>
       <c r="R154" t="s">
+        <v>511</v>
+      </c>
+      <c r="S154" t="s">
+        <v>512</v>
+      </c>
+      <c r="T154" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="155" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q155" t="s">
+        <v>78</v>
+      </c>
+      <c r="R155" t="s">
+        <v>513</v>
+      </c>
+      <c r="S155" t="s">
+        <v>514</v>
+      </c>
+      <c r="T155" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="156" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q156" t="s">
+        <v>78</v>
+      </c>
+      <c r="R156" t="s">
+        <v>515</v>
+      </c>
+      <c r="S156" t="s">
+        <v>516</v>
+      </c>
+      <c r="T156" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="157" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q157" t="s">
+        <v>78</v>
+      </c>
+      <c r="R157" t="s">
+        <v>517</v>
+      </c>
+      <c r="S157" t="s">
+        <v>518</v>
+      </c>
+      <c r="T157" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="158" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q158" t="s">
+        <v>78</v>
+      </c>
+      <c r="R158" t="s">
+        <v>519</v>
+      </c>
+      <c r="S158" t="s">
+        <v>520</v>
+      </c>
+      <c r="T158" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="159" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q159" t="s">
+        <v>78</v>
+      </c>
+      <c r="R159" t="s">
+        <v>142</v>
+      </c>
+      <c r="S159" t="s">
+        <v>143</v>
+      </c>
+      <c r="T159" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="160" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q160" t="s">
+        <v>78</v>
+      </c>
+      <c r="R160" t="s">
+        <v>521</v>
+      </c>
+      <c r="S160" t="s">
+        <v>522</v>
+      </c>
+      <c r="T160" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="161" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q161" t="s">
+        <v>78</v>
+      </c>
+      <c r="R161" t="s">
+        <v>302</v>
+      </c>
+      <c r="S161" t="s">
+        <v>303</v>
+      </c>
+      <c r="T161" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="162" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q162" t="s">
+        <v>78</v>
+      </c>
+      <c r="R162" t="s">
+        <v>148</v>
+      </c>
+      <c r="S162" t="s">
+        <v>149</v>
+      </c>
+      <c r="T162" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="163" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q163" t="s">
+        <v>78</v>
+      </c>
+      <c r="R163" t="s">
+        <v>523</v>
+      </c>
+      <c r="S163" t="s">
+        <v>524</v>
+      </c>
+      <c r="T163" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="164" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q164" t="s">
+        <v>78</v>
+      </c>
+      <c r="R164" t="s">
+        <v>196</v>
+      </c>
+      <c r="S164" t="s">
+        <v>197</v>
+      </c>
+      <c r="T164" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="165" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q165" t="s">
+        <v>78</v>
+      </c>
+      <c r="R165" t="s">
+        <v>525</v>
+      </c>
+      <c r="S165" t="s">
+        <v>526</v>
+      </c>
+      <c r="T165" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="166" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q166" t="s">
+        <v>78</v>
+      </c>
+      <c r="R166" t="s">
+        <v>138</v>
+      </c>
+      <c r="S166" t="s">
+        <v>139</v>
+      </c>
+      <c r="T166" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="167" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q167" t="s">
+        <v>78</v>
+      </c>
+      <c r="R167" t="s">
+        <v>152</v>
+      </c>
+      <c r="S167" t="s">
+        <v>153</v>
+      </c>
+      <c r="T167" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="168" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q168" t="s">
+        <v>78</v>
+      </c>
+      <c r="R168" t="s">
+        <v>527</v>
+      </c>
+      <c r="S168" t="s">
+        <v>528</v>
+      </c>
+      <c r="T168" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="169" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q169" t="s">
+        <v>78</v>
+      </c>
+      <c r="R169" t="s">
+        <v>170</v>
+      </c>
+      <c r="S169" t="s">
+        <v>171</v>
+      </c>
+      <c r="T169" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="170" spans="17:20" x14ac:dyDescent="0.45">
+      <c r="Q170" t="s">
+        <v>78</v>
+      </c>
+      <c r="R170" t="s">
         <v>158</v>
       </c>
-      <c r="S154" t="s">
+      <c r="S170" t="s">
         <v>159</v>
       </c>
-      <c r="T154" t="s">
+      <c r="T170" t="s">
         <v>322</v>
       </c>
     </row>

--- a/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAECD1E6-C86F-406E-809D-6BE10F495E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0122FC69-DABE-468A-9524-F6309F140F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="451">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -1009,12 +1009,6 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>w11285720-380</t>
-  </si>
-  <si>
-    <t>at grid node - w11285720-380</t>
-  </si>
-  <si>
     <t>w18629425-380</t>
   </si>
   <si>
@@ -1105,12 +1099,6 @@
     <t>at grid node - w24757392-380</t>
   </si>
   <si>
-    <t>w24921206-380</t>
-  </si>
-  <si>
-    <t>at grid node - w24921206-380</t>
-  </si>
-  <si>
     <t>w25306752-380</t>
   </si>
   <si>
@@ -1159,42 +1147,18 @@
     <t>at grid node - w27149550-380</t>
   </si>
   <si>
-    <t>w28327356-380</t>
-  </si>
-  <si>
-    <t>at grid node - w28327356-380</t>
-  </si>
-  <si>
     <t>w29713902-380</t>
   </si>
   <si>
     <t>at grid node - w29713902-380</t>
   </si>
   <si>
-    <t>w30040568-380</t>
-  </si>
-  <si>
-    <t>at grid node - w30040568-380</t>
-  </si>
-  <si>
-    <t>w30132758-380</t>
-  </si>
-  <si>
-    <t>at grid node - w30132758-380</t>
-  </si>
-  <si>
     <t>w30613895-380</t>
   </si>
   <si>
     <t>at grid node - w30613895-380</t>
   </si>
   <si>
-    <t>w31131320-380</t>
-  </si>
-  <si>
-    <t>at grid node - w31131320-380</t>
-  </si>
-  <si>
     <t>w31131325-380</t>
   </si>
   <si>
@@ -1213,108 +1177,24 @@
     <t>at grid node - w32076853-380</t>
   </si>
   <si>
-    <t>w32472806-380</t>
-  </si>
-  <si>
-    <t>at grid node - w32472806-380</t>
-  </si>
-  <si>
-    <t>w32904794-380</t>
-  </si>
-  <si>
-    <t>at grid node - w32904794-380</t>
-  </si>
-  <si>
     <t>w33816726-380</t>
   </si>
   <si>
     <t>at grid node - w33816726-380</t>
   </si>
   <si>
-    <t>w35763480-380</t>
-  </si>
-  <si>
-    <t>at grid node - w35763480-380</t>
-  </si>
-  <si>
-    <t>w37764852-380</t>
-  </si>
-  <si>
-    <t>at grid node - w37764852-380</t>
-  </si>
-  <si>
     <t>w38661452-380</t>
   </si>
   <si>
     <t>at grid node - w38661452-380</t>
   </si>
   <si>
-    <t>w41389594-380</t>
-  </si>
-  <si>
-    <t>at grid node - w41389594-380</t>
-  </si>
-  <si>
-    <t>w42050342-380</t>
-  </si>
-  <si>
-    <t>at grid node - w42050342-380</t>
-  </si>
-  <si>
-    <t>w42488850-380</t>
-  </si>
-  <si>
-    <t>at grid node - w42488850-380</t>
-  </si>
-  <si>
-    <t>w42560068-380</t>
-  </si>
-  <si>
-    <t>at grid node - w42560068-380</t>
-  </si>
-  <si>
-    <t>w42736239-380</t>
-  </si>
-  <si>
-    <t>at grid node - w42736239-380</t>
-  </si>
-  <si>
-    <t>w42797575-380</t>
-  </si>
-  <si>
-    <t>at grid node - w42797575-380</t>
-  </si>
-  <si>
     <t>w43688805-380</t>
   </si>
   <si>
     <t>at grid node - w43688805-380</t>
   </si>
   <si>
-    <t>w691662101-380</t>
-  </si>
-  <si>
-    <t>at grid node - w691662101-380</t>
-  </si>
-  <si>
-    <t>w57727004-380</t>
-  </si>
-  <si>
-    <t>at grid node - w57727004-380</t>
-  </si>
-  <si>
-    <t>w59026005-380</t>
-  </si>
-  <si>
-    <t>at grid node - w59026005-380</t>
-  </si>
-  <si>
-    <t>w78441561-380</t>
-  </si>
-  <si>
-    <t>at grid node - w78441561-380</t>
-  </si>
-  <si>
     <t>w87767098-380</t>
   </si>
   <si>
@@ -1339,12 +1219,6 @@
     <t>at grid node - w954305865-380</t>
   </si>
   <si>
-    <t>w143854536-380</t>
-  </si>
-  <si>
-    <t>at grid node - w143854536-380</t>
-  </si>
-  <si>
     <t>w143882655-380</t>
   </si>
   <si>
@@ -1363,18 +1237,6 @@
     <t>at grid node - w149256409-380</t>
   </si>
   <si>
-    <t>w152107815-380</t>
-  </si>
-  <si>
-    <t>at grid node - w152107815-380</t>
-  </si>
-  <si>
-    <t>w152403632-380</t>
-  </si>
-  <si>
-    <t>at grid node - w152403632-380</t>
-  </si>
-  <si>
     <t>w156673636-380</t>
   </si>
   <si>
@@ -1405,12 +1267,6 @@
     <t>at grid node - w177829920-380</t>
   </si>
   <si>
-    <t>w198448981-380</t>
-  </si>
-  <si>
-    <t>at grid node - w198448981-380</t>
-  </si>
-  <si>
     <t>w202747445-380</t>
   </si>
   <si>
@@ -1429,18 +1285,6 @@
     <t>at grid node - w395847307-380</t>
   </si>
   <si>
-    <t>w941453716-380</t>
-  </si>
-  <si>
-    <t>at grid node - w941453716-380</t>
-  </si>
-  <si>
-    <t>w941805476-380</t>
-  </si>
-  <si>
-    <t>at grid node - w941805476-380</t>
-  </si>
-  <si>
     <t>w942771541-380</t>
   </si>
   <si>
@@ -1465,42 +1309,12 @@
     <t>at grid node - w952004951-380</t>
   </si>
   <si>
-    <t>w952346322-380</t>
-  </si>
-  <si>
-    <t>at grid node - w952346322-380</t>
-  </si>
-  <si>
-    <t>w1102237380-380</t>
-  </si>
-  <si>
-    <t>at grid node - w1102237380-380</t>
-  </si>
-  <si>
     <t>w1128250704-380</t>
   </si>
   <si>
     <t>at grid node - w1128250704-380</t>
   </si>
   <si>
-    <t>DE176-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE176-380</t>
-  </si>
-  <si>
-    <t>DE143-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE143-380</t>
-  </si>
-  <si>
-    <t>DE170-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE170-380</t>
-  </si>
-  <si>
     <t>DE68-380</t>
   </si>
   <si>
@@ -1519,12 +1333,6 @@
     <t>at grid node - DE227-380</t>
   </si>
   <si>
-    <t>DE230-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE230-380</t>
-  </si>
-  <si>
     <t>w42861703-380</t>
   </si>
   <si>
@@ -1549,12 +1357,6 @@
     <t>at grid node - w91854336-380</t>
   </si>
   <si>
-    <t>DE95-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE95-380</t>
-  </si>
-  <si>
     <t>DE134-380</t>
   </si>
   <si>
@@ -1567,42 +1369,12 @@
     <t>at grid node - DE221-380</t>
   </si>
   <si>
-    <t>DE124-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE124-380</t>
-  </si>
-  <si>
-    <t>DE135-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE135-380</t>
-  </si>
-  <si>
-    <t>DE58-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE58-380</t>
-  </si>
-  <si>
     <t>DE214-380</t>
   </si>
   <si>
     <t>at grid node - DE214-380</t>
   </si>
   <si>
-    <t>DE57-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE57-380</t>
-  </si>
-  <si>
-    <t>DE69-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE69-380</t>
-  </si>
-  <si>
     <t>DE172-380</t>
   </si>
   <si>
@@ -1619,12 +1391,6 @@
   </si>
   <si>
     <t>at grid node - DE140-380</t>
-  </si>
-  <si>
-    <t>DE209-380</t>
-  </si>
-  <si>
-    <t>at grid node - DE209-380</t>
   </si>
 </sst>
 </file>
@@ -1952,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T170"/>
+  <dimension ref="B3:T130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
@@ -2331,10 +2097,10 @@
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>331</v>
+        <v>190</v>
       </c>
       <c r="S16" t="s">
-        <v>332</v>
+        <v>191</v>
       </c>
       <c r="T16" t="s">
         <v>322</v>
@@ -2381,10 +2147,10 @@
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="S17" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
       <c r="T17" t="s">
         <v>322</v>
@@ -2631,10 +2397,10 @@
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>341</v>
+        <v>192</v>
       </c>
       <c r="S22" t="s">
-        <v>342</v>
+        <v>193</v>
       </c>
       <c r="T22" t="s">
         <v>322</v>
@@ -2681,10 +2447,10 @@
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>192</v>
+        <v>122</v>
       </c>
       <c r="S23" t="s">
-        <v>193</v>
+        <v>123</v>
       </c>
       <c r="T23" t="s">
         <v>322</v>
@@ -2731,10 +2497,10 @@
         <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>122</v>
+        <v>341</v>
       </c>
       <c r="S24" t="s">
-        <v>123</v>
+        <v>342</v>
       </c>
       <c r="T24" t="s">
         <v>322</v>
@@ -2831,10 +2597,10 @@
         <v>78</v>
       </c>
       <c r="R26" t="s">
-        <v>345</v>
+        <v>146</v>
       </c>
       <c r="S26" t="s">
-        <v>346</v>
+        <v>147</v>
       </c>
       <c r="T26" t="s">
         <v>322</v>
@@ -2881,10 +2647,10 @@
         <v>78</v>
       </c>
       <c r="R27" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="S27" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="T27" t="s">
         <v>322</v>
@@ -2931,10 +2697,10 @@
         <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>202</v>
+        <v>345</v>
       </c>
       <c r="S28" t="s">
-        <v>203</v>
+        <v>346</v>
       </c>
       <c r="T28" t="s">
         <v>322</v>
@@ -3031,10 +2797,10 @@
         <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="S30" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="T30" t="s">
         <v>322</v>
@@ -3081,10 +2847,10 @@
         <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="S31" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="T31" t="s">
         <v>322</v>
@@ -3131,10 +2897,10 @@
         <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>314</v>
+        <v>90</v>
       </c>
       <c r="S32" t="s">
-        <v>315</v>
+        <v>91</v>
       </c>
       <c r="T32" t="s">
         <v>322</v>
@@ -3181,10 +2947,10 @@
         <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>351</v>
+        <v>118</v>
       </c>
       <c r="S33" t="s">
-        <v>352</v>
+        <v>119</v>
       </c>
       <c r="T33" t="s">
         <v>322</v>
@@ -3231,10 +2997,10 @@
         <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>90</v>
+        <v>351</v>
       </c>
       <c r="S34" t="s">
-        <v>91</v>
+        <v>352</v>
       </c>
       <c r="T34" t="s">
         <v>322</v>
@@ -3281,10 +3047,10 @@
         <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>118</v>
+        <v>284</v>
       </c>
       <c r="S35" t="s">
-        <v>119</v>
+        <v>285</v>
       </c>
       <c r="T35" t="s">
         <v>322</v>
@@ -3407,10 +3173,10 @@
         <v>78</v>
       </c>
       <c r="R38" t="s">
-        <v>284</v>
+        <v>357</v>
       </c>
       <c r="S38" t="s">
-        <v>285</v>
+        <v>358</v>
       </c>
       <c r="T38" t="s">
         <v>322</v>
@@ -3445,10 +3211,10 @@
         <v>78</v>
       </c>
       <c r="R39" t="s">
-        <v>357</v>
+        <v>234</v>
       </c>
       <c r="S39" t="s">
-        <v>358</v>
+        <v>235</v>
       </c>
       <c r="T39" t="s">
         <v>322</v>
@@ -3559,10 +3325,10 @@
         <v>78</v>
       </c>
       <c r="R42" t="s">
-        <v>234</v>
+        <v>363</v>
       </c>
       <c r="S42" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
       <c r="T42" t="s">
         <v>322</v>
@@ -3597,10 +3363,10 @@
         <v>78</v>
       </c>
       <c r="R43" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S43" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="T43" t="s">
         <v>322</v>
@@ -3635,10 +3401,10 @@
         <v>78</v>
       </c>
       <c r="R44" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S44" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="T44" t="s">
         <v>322</v>
@@ -3673,10 +3439,10 @@
         <v>78</v>
       </c>
       <c r="R45" t="s">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="S45" t="s">
-        <v>368</v>
+        <v>252</v>
       </c>
       <c r="T45" t="s">
         <v>322</v>
@@ -3711,10 +3477,10 @@
         <v>78</v>
       </c>
       <c r="R46" t="s">
-        <v>369</v>
+        <v>290</v>
       </c>
       <c r="S46" t="s">
-        <v>370</v>
+        <v>291</v>
       </c>
       <c r="T46" t="s">
         <v>322</v>
@@ -3749,10 +3515,10 @@
         <v>78</v>
       </c>
       <c r="R47" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="S47" t="s">
-        <v>244</v>
+        <v>133</v>
       </c>
       <c r="T47" t="s">
         <v>322</v>
@@ -3787,10 +3553,10 @@
         <v>78</v>
       </c>
       <c r="R48" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="S48" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="T48" t="s">
         <v>322</v>
@@ -3825,10 +3591,10 @@
         <v>78</v>
       </c>
       <c r="R49" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="S49" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="T49" t="s">
         <v>322</v>
@@ -3863,10 +3629,10 @@
         <v>78</v>
       </c>
       <c r="R50" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="S50" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="T50" t="s">
         <v>322</v>
@@ -3901,10 +3667,10 @@
         <v>78</v>
       </c>
       <c r="R51" t="s">
-        <v>251</v>
+        <v>373</v>
       </c>
       <c r="S51" t="s">
-        <v>252</v>
+        <v>374</v>
       </c>
       <c r="T51" t="s">
         <v>322</v>
@@ -3939,10 +3705,10 @@
         <v>78</v>
       </c>
       <c r="R52" t="s">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="S52" t="s">
-        <v>291</v>
+        <v>376</v>
       </c>
       <c r="T52" t="s">
         <v>322</v>
@@ -3977,10 +3743,10 @@
         <v>78</v>
       </c>
       <c r="R53" t="s">
-        <v>132</v>
+        <v>377</v>
       </c>
       <c r="S53" t="s">
-        <v>133</v>
+        <v>378</v>
       </c>
       <c r="T53" t="s">
         <v>322</v>
@@ -4015,10 +3781,10 @@
         <v>78</v>
       </c>
       <c r="R54" t="s">
-        <v>128</v>
+        <v>379</v>
       </c>
       <c r="S54" t="s">
-        <v>129</v>
+        <v>380</v>
       </c>
       <c r="T54" t="s">
         <v>322</v>
@@ -4053,10 +3819,10 @@
         <v>78</v>
       </c>
       <c r="R55" t="s">
-        <v>375</v>
+        <v>144</v>
       </c>
       <c r="S55" t="s">
-        <v>376</v>
+        <v>145</v>
       </c>
       <c r="T55" t="s">
         <v>322</v>
@@ -4091,10 +3857,10 @@
         <v>78</v>
       </c>
       <c r="R56" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="S56" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="T56" t="s">
         <v>322</v>
@@ -4129,10 +3895,10 @@
         <v>78</v>
       </c>
       <c r="R57" t="s">
-        <v>379</v>
+        <v>188</v>
       </c>
       <c r="S57" t="s">
-        <v>380</v>
+        <v>189</v>
       </c>
       <c r="T57" t="s">
         <v>322</v>
@@ -4167,10 +3933,10 @@
         <v>78</v>
       </c>
       <c r="R58" t="s">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="S58" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="T58" t="s">
         <v>322</v>
@@ -4205,10 +3971,10 @@
         <v>78</v>
       </c>
       <c r="R59" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="S59" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="T59" t="s">
         <v>322</v>
@@ -4243,10 +4009,10 @@
         <v>78</v>
       </c>
       <c r="R60" t="s">
-        <v>383</v>
+        <v>172</v>
       </c>
       <c r="S60" t="s">
-        <v>384</v>
+        <v>173</v>
       </c>
       <c r="T60" t="s">
         <v>322</v>
@@ -4281,10 +4047,10 @@
         <v>78</v>
       </c>
       <c r="R61" t="s">
-        <v>385</v>
+        <v>280</v>
       </c>
       <c r="S61" t="s">
-        <v>386</v>
+        <v>281</v>
       </c>
       <c r="T61" t="s">
         <v>322</v>
@@ -4319,10 +4085,10 @@
         <v>78</v>
       </c>
       <c r="R62" t="s">
-        <v>387</v>
+        <v>198</v>
       </c>
       <c r="S62" t="s">
-        <v>388</v>
+        <v>199</v>
       </c>
       <c r="T62" t="s">
         <v>322</v>
@@ -4357,10 +4123,10 @@
         <v>78</v>
       </c>
       <c r="R63" t="s">
-        <v>389</v>
+        <v>86</v>
       </c>
       <c r="S63" t="s">
-        <v>390</v>
+        <v>87</v>
       </c>
       <c r="T63" t="s">
         <v>322</v>
@@ -4395,10 +4161,10 @@
         <v>78</v>
       </c>
       <c r="R64" t="s">
-        <v>391</v>
+        <v>166</v>
       </c>
       <c r="S64" t="s">
-        <v>392</v>
+        <v>167</v>
       </c>
       <c r="T64" t="s">
         <v>322</v>
@@ -4433,10 +4199,10 @@
         <v>78</v>
       </c>
       <c r="R65" t="s">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="S65" t="s">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="T65" t="s">
         <v>322</v>
@@ -4471,10 +4237,10 @@
         <v>78</v>
       </c>
       <c r="R66" t="s">
-        <v>288</v>
+        <v>385</v>
       </c>
       <c r="S66" t="s">
-        <v>289</v>
+        <v>386</v>
       </c>
       <c r="T66" t="s">
         <v>322</v>
@@ -4509,10 +4275,10 @@
         <v>78</v>
       </c>
       <c r="R67" t="s">
-        <v>395</v>
+        <v>100</v>
       </c>
       <c r="S67" t="s">
-        <v>396</v>
+        <v>101</v>
       </c>
       <c r="T67" t="s">
         <v>322</v>
@@ -4547,10 +4313,10 @@
         <v>78</v>
       </c>
       <c r="R68" t="s">
-        <v>144</v>
+        <v>387</v>
       </c>
       <c r="S68" t="s">
-        <v>145</v>
+        <v>388</v>
       </c>
       <c r="T68" t="s">
         <v>322</v>
@@ -4585,10 +4351,10 @@
         <v>78</v>
       </c>
       <c r="R69" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="S69" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="T69" t="s">
         <v>322</v>
@@ -4623,10 +4389,10 @@
         <v>78</v>
       </c>
       <c r="R70" t="s">
-        <v>88</v>
+        <v>391</v>
       </c>
       <c r="S70" t="s">
-        <v>89</v>
+        <v>392</v>
       </c>
       <c r="T70" t="s">
         <v>322</v>
@@ -4661,10 +4427,10 @@
         <v>78</v>
       </c>
       <c r="R71" t="s">
-        <v>399</v>
+        <v>310</v>
       </c>
       <c r="S71" t="s">
-        <v>400</v>
+        <v>311</v>
       </c>
       <c r="T71" t="s">
         <v>322</v>
@@ -4699,10 +4465,10 @@
         <v>78</v>
       </c>
       <c r="R72" t="s">
-        <v>401</v>
+        <v>136</v>
       </c>
       <c r="S72" t="s">
-        <v>402</v>
+        <v>137</v>
       </c>
       <c r="T72" t="s">
         <v>322</v>
@@ -4737,10 +4503,10 @@
         <v>78</v>
       </c>
       <c r="R73" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="S73" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="T73" t="s">
         <v>322</v>
@@ -4775,10 +4541,10 @@
         <v>78</v>
       </c>
       <c r="R74" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="S74" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="T74" t="s">
         <v>322</v>
@@ -4813,10 +4579,10 @@
         <v>78</v>
       </c>
       <c r="R75" t="s">
-        <v>188</v>
+        <v>397</v>
       </c>
       <c r="S75" t="s">
-        <v>189</v>
+        <v>398</v>
       </c>
       <c r="T75" t="s">
         <v>322</v>
@@ -4851,10 +4617,10 @@
         <v>78</v>
       </c>
       <c r="R76" t="s">
-        <v>407</v>
+        <v>286</v>
       </c>
       <c r="S76" t="s">
-        <v>408</v>
+        <v>287</v>
       </c>
       <c r="T76" t="s">
         <v>322</v>
@@ -4889,10 +4655,10 @@
         <v>78</v>
       </c>
       <c r="R77" t="s">
-        <v>409</v>
+        <v>176</v>
       </c>
       <c r="S77" t="s">
-        <v>410</v>
+        <v>177</v>
       </c>
       <c r="T77" t="s">
         <v>322</v>
@@ -4927,10 +4693,10 @@
         <v>78</v>
       </c>
       <c r="R78" t="s">
-        <v>411</v>
+        <v>212</v>
       </c>
       <c r="S78" t="s">
-        <v>412</v>
+        <v>213</v>
       </c>
       <c r="T78" t="s">
         <v>322</v>
@@ -4965,10 +4731,10 @@
         <v>78</v>
       </c>
       <c r="R79" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="S79" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="T79" t="s">
         <v>322</v>
@@ -5003,10 +4769,10 @@
         <v>78</v>
       </c>
       <c r="R80" t="s">
-        <v>267</v>
+        <v>401</v>
       </c>
       <c r="S80" t="s">
-        <v>268</v>
+        <v>402</v>
       </c>
       <c r="T80" t="s">
         <v>322</v>
@@ -5041,10 +4807,10 @@
         <v>78</v>
       </c>
       <c r="R81" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="S81" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="T81" t="s">
         <v>322</v>
@@ -5079,10 +4845,10 @@
         <v>78</v>
       </c>
       <c r="R82" t="s">
-        <v>172</v>
+        <v>405</v>
       </c>
       <c r="S82" t="s">
-        <v>173</v>
+        <v>406</v>
       </c>
       <c r="T82" t="s">
         <v>322</v>
@@ -5117,10 +4883,10 @@
         <v>78</v>
       </c>
       <c r="R83" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="S83" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="T83" t="s">
         <v>322</v>
@@ -5155,10 +4921,10 @@
         <v>78</v>
       </c>
       <c r="R84" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="S84" t="s">
-        <v>281</v>
+        <v>410</v>
       </c>
       <c r="T84" t="s">
         <v>322</v>
@@ -5193,10 +4959,10 @@
         <v>78</v>
       </c>
       <c r="R85" t="s">
-        <v>198</v>
+        <v>411</v>
       </c>
       <c r="S85" t="s">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="T85" t="s">
         <v>322</v>
@@ -5231,10 +4997,10 @@
         <v>78</v>
       </c>
       <c r="R86" t="s">
-        <v>86</v>
+        <v>413</v>
       </c>
       <c r="S86" t="s">
-        <v>87</v>
+        <v>414</v>
       </c>
       <c r="T86" t="s">
         <v>322</v>
@@ -5269,10 +5035,10 @@
         <v>78</v>
       </c>
       <c r="R87" t="s">
-        <v>419</v>
+        <v>156</v>
       </c>
       <c r="S87" t="s">
-        <v>420</v>
+        <v>157</v>
       </c>
       <c r="T87" t="s">
         <v>322</v>
@@ -5307,10 +5073,10 @@
         <v>78</v>
       </c>
       <c r="R88" t="s">
-        <v>421</v>
+        <v>134</v>
       </c>
       <c r="S88" t="s">
-        <v>422</v>
+        <v>135</v>
       </c>
       <c r="T88" t="s">
         <v>322</v>
@@ -5333,10 +5099,10 @@
         <v>78</v>
       </c>
       <c r="R89" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="S89" t="s">
-        <v>167</v>
+        <v>416</v>
       </c>
       <c r="T89" t="s">
         <v>322</v>
@@ -5359,10 +5125,10 @@
         <v>78</v>
       </c>
       <c r="R90" t="s">
-        <v>269</v>
+        <v>98</v>
       </c>
       <c r="S90" t="s">
-        <v>270</v>
+        <v>99</v>
       </c>
       <c r="T90" t="s">
         <v>322</v>
@@ -5385,10 +5151,10 @@
         <v>78</v>
       </c>
       <c r="R91" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="S91" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="T91" t="s">
         <v>322</v>
@@ -5411,10 +5177,10 @@
         <v>78</v>
       </c>
       <c r="R92" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="S92" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="T92" t="s">
         <v>322</v>
@@ -5437,10 +5203,10 @@
         <v>78</v>
       </c>
       <c r="R93" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="S93" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="T93" t="s">
         <v>322</v>
@@ -5463,10 +5229,10 @@
         <v>78</v>
       </c>
       <c r="R94" t="s">
-        <v>100</v>
+        <v>421</v>
       </c>
       <c r="S94" t="s">
-        <v>101</v>
+        <v>422</v>
       </c>
       <c r="T94" t="s">
         <v>322</v>
@@ -5489,10 +5255,10 @@
         <v>78</v>
       </c>
       <c r="R95" t="s">
-        <v>427</v>
+        <v>304</v>
       </c>
       <c r="S95" t="s">
-        <v>428</v>
+        <v>305</v>
       </c>
       <c r="T95" t="s">
         <v>322</v>
@@ -5515,10 +5281,10 @@
         <v>78</v>
       </c>
       <c r="R96" t="s">
-        <v>429</v>
+        <v>312</v>
       </c>
       <c r="S96" t="s">
-        <v>430</v>
+        <v>313</v>
       </c>
       <c r="T96" t="s">
         <v>322</v>
@@ -5541,10 +5307,10 @@
         <v>78</v>
       </c>
       <c r="R97" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="S97" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="T97" t="s">
         <v>322</v>
@@ -5567,10 +5333,10 @@
         <v>78</v>
       </c>
       <c r="R98" t="s">
-        <v>310</v>
+        <v>124</v>
       </c>
       <c r="S98" t="s">
-        <v>311</v>
+        <v>125</v>
       </c>
       <c r="T98" t="s">
         <v>322</v>
@@ -5593,10 +5359,10 @@
         <v>78</v>
       </c>
       <c r="R99" t="s">
-        <v>136</v>
+        <v>425</v>
       </c>
       <c r="S99" t="s">
-        <v>137</v>
+        <v>426</v>
       </c>
       <c r="T99" t="s">
         <v>322</v>
@@ -5619,10 +5385,10 @@
         <v>78</v>
       </c>
       <c r="R100" t="s">
-        <v>433</v>
+        <v>162</v>
       </c>
       <c r="S100" t="s">
-        <v>434</v>
+        <v>163</v>
       </c>
       <c r="T100" t="s">
         <v>322</v>
@@ -5645,10 +5411,10 @@
         <v>78</v>
       </c>
       <c r="R101" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="S101" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="T101" t="s">
         <v>322</v>
@@ -5671,10 +5437,10 @@
         <v>78</v>
       </c>
       <c r="R102" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="S102" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="T102" t="s">
         <v>322</v>
@@ -5697,10 +5463,10 @@
         <v>78</v>
       </c>
       <c r="R103" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="S103" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="T103" t="s">
         <v>322</v>
@@ -5723,10 +5489,10 @@
         <v>78</v>
       </c>
       <c r="R104" t="s">
-        <v>286</v>
+        <v>433</v>
       </c>
       <c r="S104" t="s">
-        <v>287</v>
+        <v>434</v>
       </c>
       <c r="T104" t="s">
         <v>322</v>
@@ -5749,10 +5515,10 @@
         <v>78</v>
       </c>
       <c r="R105" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="S105" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="T105" t="s">
         <v>322</v>
@@ -5775,10 +5541,10 @@
         <v>78</v>
       </c>
       <c r="R106" t="s">
-        <v>176</v>
+        <v>437</v>
       </c>
       <c r="S106" t="s">
-        <v>177</v>
+        <v>438</v>
       </c>
       <c r="T106" t="s">
         <v>322</v>
@@ -5801,10 +5567,10 @@
         <v>78</v>
       </c>
       <c r="R107" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="S107" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="T107" t="s">
         <v>322</v>
@@ -5827,10 +5593,10 @@
         <v>78</v>
       </c>
       <c r="R108" t="s">
-        <v>212</v>
+        <v>441</v>
       </c>
       <c r="S108" t="s">
-        <v>213</v>
+        <v>442</v>
       </c>
       <c r="T108" t="s">
         <v>322</v>
@@ -5853,10 +5619,10 @@
         <v>78</v>
       </c>
       <c r="R109" t="s">
-        <v>445</v>
+        <v>306</v>
       </c>
       <c r="S109" t="s">
-        <v>446</v>
+        <v>307</v>
       </c>
       <c r="T109" t="s">
         <v>322</v>
@@ -5879,10 +5645,10 @@
         <v>78</v>
       </c>
       <c r="R110" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="S110" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="T110" t="s">
         <v>322</v>
@@ -5905,10 +5671,10 @@
         <v>78</v>
       </c>
       <c r="R111" t="s">
-        <v>449</v>
+        <v>142</v>
       </c>
       <c r="S111" t="s">
-        <v>450</v>
+        <v>143</v>
       </c>
       <c r="T111" t="s">
         <v>322</v>
@@ -5931,10 +5697,10 @@
         <v>78</v>
       </c>
       <c r="R112" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="S112" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="T112" t="s">
         <v>322</v>
@@ -5957,10 +5723,10 @@
         <v>78</v>
       </c>
       <c r="R113" t="s">
-        <v>453</v>
+        <v>302</v>
       </c>
       <c r="S113" t="s">
-        <v>454</v>
+        <v>303</v>
       </c>
       <c r="T113" t="s">
         <v>322</v>
@@ -5983,10 +5749,10 @@
         <v>78</v>
       </c>
       <c r="R114" t="s">
-        <v>455</v>
+        <v>148</v>
       </c>
       <c r="S114" t="s">
-        <v>456</v>
+        <v>149</v>
       </c>
       <c r="T114" t="s">
         <v>322</v>
@@ -6009,10 +5775,10 @@
         <v>78</v>
       </c>
       <c r="R115" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="S115" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="T115" t="s">
         <v>322</v>
@@ -6035,10 +5801,10 @@
         <v>78</v>
       </c>
       <c r="R116" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="S116" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="T116" t="s">
         <v>322</v>
@@ -6061,10 +5827,10 @@
         <v>78</v>
       </c>
       <c r="R117" t="s">
-        <v>461</v>
+        <v>138</v>
       </c>
       <c r="S117" t="s">
-        <v>462</v>
+        <v>139</v>
       </c>
       <c r="T117" t="s">
         <v>322</v>
@@ -6087,10 +5853,10 @@
         <v>78</v>
       </c>
       <c r="R118" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S118" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="T118" t="s">
         <v>322</v>
@@ -6113,10 +5879,10 @@
         <v>78</v>
       </c>
       <c r="R119" t="s">
-        <v>316</v>
+        <v>170</v>
       </c>
       <c r="S119" t="s">
-        <v>317</v>
+        <v>171</v>
       </c>
       <c r="T119" t="s">
         <v>322</v>
@@ -6139,10 +5905,10 @@
         <v>78</v>
       </c>
       <c r="R120" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="S120" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="T120" t="s">
         <v>322</v>
@@ -6161,18 +5927,6 @@
       <c r="O121" t="s">
         <v>279</v>
       </c>
-      <c r="Q121" t="s">
-        <v>78</v>
-      </c>
-      <c r="R121" t="s">
-        <v>245</v>
-      </c>
-      <c r="S121" t="s">
-        <v>246</v>
-      </c>
-      <c r="T121" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="122" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L122" t="s">
@@ -6187,18 +5941,6 @@
       <c r="O122" t="s">
         <v>279</v>
       </c>
-      <c r="Q122" t="s">
-        <v>78</v>
-      </c>
-      <c r="R122" t="s">
-        <v>134</v>
-      </c>
-      <c r="S122" t="s">
-        <v>135</v>
-      </c>
-      <c r="T122" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="123" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L123" t="s">
@@ -6213,18 +5955,6 @@
       <c r="O123" t="s">
         <v>279</v>
       </c>
-      <c r="Q123" t="s">
-        <v>78</v>
-      </c>
-      <c r="R123" t="s">
-        <v>463</v>
-      </c>
-      <c r="S123" t="s">
-        <v>464</v>
-      </c>
-      <c r="T123" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="124" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L124" t="s">
@@ -6239,18 +5969,6 @@
       <c r="O124" t="s">
         <v>279</v>
       </c>
-      <c r="Q124" t="s">
-        <v>78</v>
-      </c>
-      <c r="R124" t="s">
-        <v>465</v>
-      </c>
-      <c r="S124" t="s">
-        <v>466</v>
-      </c>
-      <c r="T124" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="125" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L125" t="s">
@@ -6265,18 +5983,6 @@
       <c r="O125" t="s">
         <v>279</v>
       </c>
-      <c r="Q125" t="s">
-        <v>78</v>
-      </c>
-      <c r="R125" t="s">
-        <v>467</v>
-      </c>
-      <c r="S125" t="s">
-        <v>468</v>
-      </c>
-      <c r="T125" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="126" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L126" t="s">
@@ -6291,18 +5997,6 @@
       <c r="O126" t="s">
         <v>279</v>
       </c>
-      <c r="Q126" t="s">
-        <v>78</v>
-      </c>
-      <c r="R126" t="s">
-        <v>98</v>
-      </c>
-      <c r="S126" t="s">
-        <v>99</v>
-      </c>
-      <c r="T126" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="127" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L127" t="s">
@@ -6317,18 +6011,6 @@
       <c r="O127" t="s">
         <v>279</v>
       </c>
-      <c r="Q127" t="s">
-        <v>78</v>
-      </c>
-      <c r="R127" t="s">
-        <v>102</v>
-      </c>
-      <c r="S127" t="s">
-        <v>103</v>
-      </c>
-      <c r="T127" t="s">
-        <v>322</v>
-      </c>
     </row>
     <row r="128" spans="12:20" x14ac:dyDescent="0.45">
       <c r="L128" t="s">
@@ -6343,20 +6025,8 @@
       <c r="O128" t="s">
         <v>279</v>
       </c>
-      <c r="Q128" t="s">
-        <v>78</v>
-      </c>
-      <c r="R128" t="s">
-        <v>469</v>
-      </c>
-      <c r="S128" t="s">
-        <v>470</v>
-      </c>
-      <c r="T128" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="129" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="129" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L129" t="s">
         <v>78</v>
       </c>
@@ -6369,20 +6039,8 @@
       <c r="O129" t="s">
         <v>279</v>
       </c>
-      <c r="Q129" t="s">
-        <v>78</v>
-      </c>
-      <c r="R129" t="s">
-        <v>471</v>
-      </c>
-      <c r="S129" t="s">
-        <v>472</v>
-      </c>
-      <c r="T129" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="130" spans="12:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="130" spans="12:15" x14ac:dyDescent="0.45">
       <c r="L130" t="s">
         <v>78</v>
       </c>
@@ -6394,578 +6052,6 @@
       </c>
       <c r="O130" t="s">
         <v>279</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>78</v>
-      </c>
-      <c r="R130" t="s">
-        <v>473</v>
-      </c>
-      <c r="S130" t="s">
-        <v>474</v>
-      </c>
-      <c r="T130" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="131" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q131" t="s">
-        <v>78</v>
-      </c>
-      <c r="R131" t="s">
-        <v>475</v>
-      </c>
-      <c r="S131" t="s">
-        <v>476</v>
-      </c>
-      <c r="T131" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="132" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q132" t="s">
-        <v>78</v>
-      </c>
-      <c r="R132" t="s">
-        <v>304</v>
-      </c>
-      <c r="S132" t="s">
-        <v>305</v>
-      </c>
-      <c r="T132" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="133" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q133" t="s">
-        <v>78</v>
-      </c>
-      <c r="R133" t="s">
-        <v>312</v>
-      </c>
-      <c r="S133" t="s">
-        <v>313</v>
-      </c>
-      <c r="T133" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="134" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q134" t="s">
-        <v>78</v>
-      </c>
-      <c r="R134" t="s">
-        <v>477</v>
-      </c>
-      <c r="S134" t="s">
-        <v>478</v>
-      </c>
-      <c r="T134" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="135" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q135" t="s">
-        <v>78</v>
-      </c>
-      <c r="R135" t="s">
-        <v>479</v>
-      </c>
-      <c r="S135" t="s">
-        <v>480</v>
-      </c>
-      <c r="T135" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="136" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q136" t="s">
-        <v>78</v>
-      </c>
-      <c r="R136" t="s">
-        <v>124</v>
-      </c>
-      <c r="S136" t="s">
-        <v>125</v>
-      </c>
-      <c r="T136" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="137" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q137" t="s">
-        <v>78</v>
-      </c>
-      <c r="R137" t="s">
-        <v>481</v>
-      </c>
-      <c r="S137" t="s">
-        <v>482</v>
-      </c>
-      <c r="T137" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="138" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q138" t="s">
-        <v>78</v>
-      </c>
-      <c r="R138" t="s">
-        <v>483</v>
-      </c>
-      <c r="S138" t="s">
-        <v>484</v>
-      </c>
-      <c r="T138" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="139" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q139" t="s">
-        <v>78</v>
-      </c>
-      <c r="R139" t="s">
-        <v>485</v>
-      </c>
-      <c r="S139" t="s">
-        <v>486</v>
-      </c>
-      <c r="T139" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="140" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q140" t="s">
-        <v>78</v>
-      </c>
-      <c r="R140" t="s">
-        <v>487</v>
-      </c>
-      <c r="S140" t="s">
-        <v>488</v>
-      </c>
-      <c r="T140" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="141" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q141" t="s">
-        <v>78</v>
-      </c>
-      <c r="R141" t="s">
-        <v>162</v>
-      </c>
-      <c r="S141" t="s">
-        <v>163</v>
-      </c>
-      <c r="T141" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="142" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q142" t="s">
-        <v>78</v>
-      </c>
-      <c r="R142" t="s">
-        <v>489</v>
-      </c>
-      <c r="S142" t="s">
-        <v>490</v>
-      </c>
-      <c r="T142" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="143" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q143" t="s">
-        <v>78</v>
-      </c>
-      <c r="R143" t="s">
-        <v>491</v>
-      </c>
-      <c r="S143" t="s">
-        <v>492</v>
-      </c>
-      <c r="T143" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="144" spans="12:20" x14ac:dyDescent="0.45">
-      <c r="Q144" t="s">
-        <v>78</v>
-      </c>
-      <c r="R144" t="s">
-        <v>493</v>
-      </c>
-      <c r="S144" t="s">
-        <v>494</v>
-      </c>
-      <c r="T144" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="145" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q145" t="s">
-        <v>78</v>
-      </c>
-      <c r="R145" t="s">
-        <v>495</v>
-      </c>
-      <c r="S145" t="s">
-        <v>496</v>
-      </c>
-      <c r="T145" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="146" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q146" t="s">
-        <v>78</v>
-      </c>
-      <c r="R146" t="s">
-        <v>497</v>
-      </c>
-      <c r="S146" t="s">
-        <v>498</v>
-      </c>
-      <c r="T146" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="147" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q147" t="s">
-        <v>78</v>
-      </c>
-      <c r="R147" t="s">
-        <v>499</v>
-      </c>
-      <c r="S147" t="s">
-        <v>500</v>
-      </c>
-      <c r="T147" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="148" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q148" t="s">
-        <v>78</v>
-      </c>
-      <c r="R148" t="s">
-        <v>501</v>
-      </c>
-      <c r="S148" t="s">
-        <v>502</v>
-      </c>
-      <c r="T148" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="149" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q149" t="s">
-        <v>78</v>
-      </c>
-      <c r="R149" t="s">
-        <v>503</v>
-      </c>
-      <c r="S149" t="s">
-        <v>504</v>
-      </c>
-      <c r="T149" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="150" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q150" t="s">
-        <v>78</v>
-      </c>
-      <c r="R150" t="s">
-        <v>505</v>
-      </c>
-      <c r="S150" t="s">
-        <v>506</v>
-      </c>
-      <c r="T150" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="151" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q151" t="s">
-        <v>78</v>
-      </c>
-      <c r="R151" t="s">
-        <v>507</v>
-      </c>
-      <c r="S151" t="s">
-        <v>508</v>
-      </c>
-      <c r="T151" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="152" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q152" t="s">
-        <v>78</v>
-      </c>
-      <c r="R152" t="s">
-        <v>306</v>
-      </c>
-      <c r="S152" t="s">
-        <v>307</v>
-      </c>
-      <c r="T152" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="153" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q153" t="s">
-        <v>78</v>
-      </c>
-      <c r="R153" t="s">
-        <v>509</v>
-      </c>
-      <c r="S153" t="s">
-        <v>510</v>
-      </c>
-      <c r="T153" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="154" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q154" t="s">
-        <v>78</v>
-      </c>
-      <c r="R154" t="s">
-        <v>511</v>
-      </c>
-      <c r="S154" t="s">
-        <v>512</v>
-      </c>
-      <c r="T154" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="155" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q155" t="s">
-        <v>78</v>
-      </c>
-      <c r="R155" t="s">
-        <v>513</v>
-      </c>
-      <c r="S155" t="s">
-        <v>514</v>
-      </c>
-      <c r="T155" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="156" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q156" t="s">
-        <v>78</v>
-      </c>
-      <c r="R156" t="s">
-        <v>515</v>
-      </c>
-      <c r="S156" t="s">
-        <v>516</v>
-      </c>
-      <c r="T156" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="157" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q157" t="s">
-        <v>78</v>
-      </c>
-      <c r="R157" t="s">
-        <v>517</v>
-      </c>
-      <c r="S157" t="s">
-        <v>518</v>
-      </c>
-      <c r="T157" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="158" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q158" t="s">
-        <v>78</v>
-      </c>
-      <c r="R158" t="s">
-        <v>519</v>
-      </c>
-      <c r="S158" t="s">
-        <v>520</v>
-      </c>
-      <c r="T158" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="159" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q159" t="s">
-        <v>78</v>
-      </c>
-      <c r="R159" t="s">
-        <v>142</v>
-      </c>
-      <c r="S159" t="s">
-        <v>143</v>
-      </c>
-      <c r="T159" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="160" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q160" t="s">
-        <v>78</v>
-      </c>
-      <c r="R160" t="s">
-        <v>521</v>
-      </c>
-      <c r="S160" t="s">
-        <v>522</v>
-      </c>
-      <c r="T160" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="161" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q161" t="s">
-        <v>78</v>
-      </c>
-      <c r="R161" t="s">
-        <v>302</v>
-      </c>
-      <c r="S161" t="s">
-        <v>303</v>
-      </c>
-      <c r="T161" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="162" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q162" t="s">
-        <v>78</v>
-      </c>
-      <c r="R162" t="s">
-        <v>148</v>
-      </c>
-      <c r="S162" t="s">
-        <v>149</v>
-      </c>
-      <c r="T162" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="163" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q163" t="s">
-        <v>78</v>
-      </c>
-      <c r="R163" t="s">
-        <v>523</v>
-      </c>
-      <c r="S163" t="s">
-        <v>524</v>
-      </c>
-      <c r="T163" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="164" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q164" t="s">
-        <v>78</v>
-      </c>
-      <c r="R164" t="s">
-        <v>196</v>
-      </c>
-      <c r="S164" t="s">
-        <v>197</v>
-      </c>
-      <c r="T164" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="165" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q165" t="s">
-        <v>78</v>
-      </c>
-      <c r="R165" t="s">
-        <v>525</v>
-      </c>
-      <c r="S165" t="s">
-        <v>526</v>
-      </c>
-      <c r="T165" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="166" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q166" t="s">
-        <v>78</v>
-      </c>
-      <c r="R166" t="s">
-        <v>138</v>
-      </c>
-      <c r="S166" t="s">
-        <v>139</v>
-      </c>
-      <c r="T166" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="167" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q167" t="s">
-        <v>78</v>
-      </c>
-      <c r="R167" t="s">
-        <v>152</v>
-      </c>
-      <c r="S167" t="s">
-        <v>153</v>
-      </c>
-      <c r="T167" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="168" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q168" t="s">
-        <v>78</v>
-      </c>
-      <c r="R168" t="s">
-        <v>527</v>
-      </c>
-      <c r="S168" t="s">
-        <v>528</v>
-      </c>
-      <c r="T168" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="169" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q169" t="s">
-        <v>78</v>
-      </c>
-      <c r="R169" t="s">
-        <v>170</v>
-      </c>
-      <c r="S169" t="s">
-        <v>171</v>
-      </c>
-      <c r="T169" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="170" spans="17:20" x14ac:dyDescent="0.45">
-      <c r="Q170" t="s">
-        <v>78</v>
-      </c>
-      <c r="R170" t="s">
-        <v>158</v>
-      </c>
-      <c r="S170" t="s">
-        <v>159</v>
-      </c>
-      <c r="T170" t="s">
-        <v>322</v>
       </c>
     </row>
   </sheetData>
